--- a/files/九龙-长沙湾-连方II.xlsx
+++ b/files/九龙-长沙湾-连方II.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连方II 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1602,7 +1469,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1648,7 +1515,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1694,7 +1561,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1932,7 +1799,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2028,7 +1895,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2174,7 +2041,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2362,7 +2229,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2454,7 +2321,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2500,7 +2367,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2546,7 +2413,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2880,7 +2747,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3072,7 +2939,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3214,7 +3081,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3306,7 +3173,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3352,7 +3219,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3398,7 +3265,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3590,7 +3457,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3636,7 +3503,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3732,7 +3599,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3924,7 +3791,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4158,7 +4025,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4204,7 +4071,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4250,7 +4117,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4442,7 +4309,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4488,7 +4355,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4584,7 +4451,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4776,7 +4643,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4918,7 +4785,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4964,7 +4831,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -5010,7 +4877,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5056,7 +4923,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5102,7 +4969,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5198,7 +5065,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5244,7 +5111,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5290,7 +5157,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5336,7 +5203,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5432,7 +5299,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5578,7 +5445,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5624,7 +5491,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5766,7 +5633,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5812,7 +5679,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5858,7 +5725,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5904,7 +5771,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5950,7 +5817,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -6046,7 +5913,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6092,7 +5959,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6138,7 +6005,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6184,7 +6051,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6280,7 +6147,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6326,7 +6193,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6422,7 +6289,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6514,7 +6381,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6606,7 +6473,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6652,7 +6519,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6698,7 +6565,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6744,7 +6611,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6790,7 +6657,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6886,7 +6753,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6978,7 +6845,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -7024,7 +6891,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -7120,7 +6987,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7166,7 +7033,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7262,7 +7129,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7308,7 +7175,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7354,7 +7221,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7446,7 +7313,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7538,7 +7405,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7584,7 +7451,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7630,7 +7497,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7726,7 +7593,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7772,7 +7639,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7818,7 +7685,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7864,7 +7731,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7960,7 +7827,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -8006,7 +7873,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -8102,7 +7969,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -8148,7 +8015,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8194,7 +8061,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8286,7 +8153,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8332,7 +8199,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8378,7 +8245,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8424,7 +8291,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8470,7 +8337,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8566,7 +8433,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8612,7 +8479,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8658,7 +8525,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8704,7 +8571,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8800,7 +8667,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8942,7 +8809,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8988,7 +8855,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -9126,7 +8993,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9218,7 +9085,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9264,7 +9131,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9406,7 +9273,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9452,7 +9319,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9498,7 +9365,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9640,7 +9507,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9686,7 +9553,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9782,7 +9649,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9828,7 +9695,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9874,7 +9741,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9966,7 +9833,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -10012,7 +9879,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -10058,7 +9925,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -10246,7 +10113,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10292,7 +10159,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10338,7 +10205,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10384,7 +10251,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10476,7 +10343,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10522,7 +10389,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10568,7 +10435,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10614,7 +10481,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10660,7 +10527,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10706,7 +10573,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10798,7 +10665,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10844,7 +10711,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10890,7 +10757,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10936,7 +10803,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10982,7 +10849,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -11078,7 +10945,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -11124,7 +10991,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -11170,7 +11037,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11216,7 +11083,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11308,7 +11175,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11354,7 +11221,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11446,7 +11313,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11492,7 +11359,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11538,7 +11405,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11630,7 +11497,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11676,7 +11543,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11722,7 +11589,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11768,7 +11635,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11814,7 +11681,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11910,7 +11777,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11956,7 +11823,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -12002,7 +11869,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -12048,7 +11915,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -12140,7 +12007,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -12186,7 +12053,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12278,7 +12145,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12324,7 +12191,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12370,7 +12237,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12462,7 +12329,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12508,7 +12375,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12554,7 +12421,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12600,7 +12467,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12646,7 +12513,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12742,7 +12609,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12788,7 +12655,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12834,7 +12701,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12880,7 +12747,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12972,7 +12839,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -13110,7 +12977,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -13156,7 +13023,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -13202,7 +13069,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13294,7 +13161,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13340,7 +13207,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13386,7 +13253,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13432,7 +13299,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13478,7 +13345,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13574,7 +13441,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13620,7 +13487,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13666,7 +13533,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13712,7 +13579,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13804,7 +13671,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13850,7 +13717,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13942,7 +13809,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13988,7 +13855,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -14034,7 +13901,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -14126,7 +13993,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -14172,7 +14039,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14218,7 +14085,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14264,7 +14131,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14310,7 +14177,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14406,7 +14273,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14452,7 +14319,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14498,7 +14365,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14544,7 +14411,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14636,7 +14503,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14774,7 +14641,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14820,7 +14687,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14866,7 +14733,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14958,7 +14825,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -15004,7 +14871,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -15050,7 +14917,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -15096,7 +14963,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -15142,7 +15009,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -15238,7 +15105,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15284,7 +15151,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15330,7 +15197,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15376,7 +15243,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15468,7 +15335,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15606,7 +15473,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15652,7 +15519,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15698,7 +15565,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15790,7 +15657,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15836,7 +15703,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15882,7 +15749,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15928,7 +15795,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15974,7 +15841,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -16070,7 +15937,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -16116,7 +15983,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -16162,7 +16029,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16208,7 +16075,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16300,7 +16167,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16438,7 +16305,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16484,7 +16351,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16530,7 +16397,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16668,7 +16535,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16714,7 +16581,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16760,7 +16627,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16806,7 +16673,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -16902,7 +16769,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16948,7 +16815,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16994,7 +16861,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -17040,7 +16907,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -17132,7 +16999,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -17178,7 +17045,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -17270,7 +17137,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17316,7 +17183,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17454,7 +17321,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17500,7 +17367,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17546,7 +17413,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17638,7 +17505,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -17872,7 +17739,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -17968,7 +17835,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -18156,7 +18023,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -18294,7 +18161,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18362,3382 +18229,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>连方II - 连方II 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>378 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>39 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>228 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>74 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>N1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>N2</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>N6</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>N8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>N9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O6" s="16" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q6" s="16" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="R6" s="16" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="S6" s="16" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$875万
-$31,254/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 268呎 (开放式)
-$607万
-$22,657/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$907万
-$32,285/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$937万
-$33,213/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,205万
-$22,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$960万
-$27,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$586万
-$22,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$1,243万
-$34,066/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O7" s="19" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,461万
-$34,701/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q7" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$431万
-$20,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R7" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,047万
-$26,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$696万
-$19,556/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$862万
-$30,793/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$507万
-$18,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$894万
-$31,804/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$563万
-$19,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,199万
-$22,292/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$946万
-$27,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$583万
-$22,514/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$1,225万
-$33,564/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,439万
-$34,185/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q8" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$411万
-$19,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R8" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,031万
-$26,441/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$1,000万
-$28,087/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$858万
-$30,643/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$586万
-$21,963/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$889万
-$31,651/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$797万
-$28,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,193万
-$22,180/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$941万
-$27,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$499万
-$19,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M9" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$778万
-$21,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O9" s="19" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,427万
-$33,903/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q9" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$409万
-$19,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R9" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,026万
-$26,313/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S9" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$995万
-$27,944/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$743万
-$26,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$502万
-$18,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$868万
-$30,883/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$615万
-$21,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,187万
-$22,071/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$937万
-$26,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$485万
-$18,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$693万
-$18,978/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,415万
-$33,620/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$404万
-$18,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R10" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,021万
-$26,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S10" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$967万
-$27,160/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$764万
-$27,304/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$488万
-$18,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$864万
-$30,730/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$770万
-$27,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$992万
-$18,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$932万
-$26,779/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$483万
-$18,633/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M11" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$764万
-$20,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$735万
-$19,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O11" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$807万
-$19,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q11" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$523万
-$24,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R11" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,016万
-$26,054/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S11" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$962万
-$27,028/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$735万
-$26,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$697万
-$26,120/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$640万
-$22,857/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$748万
-$26,605/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$879万
-$31,160/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,443万
-$26,816/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,608万
-$26,313/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$927万
-$26,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$674万
-$26,023/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$681万
-$18,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$756万
-$20,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O12" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,147万
-$27,247/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$520万
-$24,423/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R12" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,035万
-$26,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S12" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$980万
-$27,531/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$825万
-$29,454/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$678万
-$25,386/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$637万
-$22,743/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$641万
-$22,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$759万
-$26,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$983万
-$18,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,095万
-$17,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$923万
-$26,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$671万
-$25,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$987万
-$27,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$846万
-$22,432/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,138万
-$27,021/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P13" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q13" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$518万
-$24,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R13" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,006万
-$25,795/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S13" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$953万
-$26,758/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$730万
-$26,082/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$674万
-$25,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$634万
-$22,632/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$740万
-$26,342/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$770万
-$27,319/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,428万
-$26,548/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,090万
-$17,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$918万
-$26,385/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$667万
-$25,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$978万
-$26,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$1,033万
-$27,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O14" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,128万
-$26,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q14" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$515万
-$24,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R14" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,001万
-$25,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S14" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$948万
-$26,626/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$820万
-$29,275/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$674万
-$25,236/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$921万
-$32,889/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$850万
-$30,249/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$750万
-$26,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$977万
-$18,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,893万
-$30,987/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$917万
-$26,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$667万
-$25,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M15" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$974万
-$26,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$704万
-$18,666/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,150万
-$27,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q15" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$399万
-$18,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R15" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,000万
-$25,644/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S15" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$970万
-$27,233/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$706万
-$25,221/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$667万
-$24,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$912万
-$32,561/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$732万
-$26,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$727万
-$25,777/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,413万
-$26,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,134万
-$18,561/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$908万
-$26,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$786万
-$30,359/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$961万
-$26,332/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N16" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$773万
-$20,496/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O16" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,108万
-$26,321/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P16" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q16" s="20" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$660万
-$30,967/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="R16" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$990万
-$25,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S16" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$938万
-$26,340/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$703万
-$25,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$664万
-$24,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$907万
-$32,400/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$729万
-$25,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$721万
-$25,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,406万
-$26,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$771万
-$19,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,567万
-$25,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$904万
-$25,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$609万
-$21,739/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$657万
-$25,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$954万
-$26,134/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N17" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$1,007万
-$26,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O17" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,100万
-$26,121/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P17" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q17" s="20" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$656万
-$30,812/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="R17" s="20" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$1,173万
-$30,069/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="S17" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$933万
-$26,208/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$699万
-$24,971/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 268呎 (开放式)
-$661万
-$24,668/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$903万
-$32,239/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$725万
-$25,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$757万
-$26,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,399万
-$25,998/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$913万
-$22,890/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,559万
-$25,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$899万
-$25,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$606万
-$21,632/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$654万
-$25,251/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$947万
-$25,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N18" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$684万
-$18,146/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,092万
-$25,926/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P18" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q18" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$549万
-$25,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R18" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$980万
-$25,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S18" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$928万
-$26,076/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$696万
-$24,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$658万
-$24,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$889万
-$31,757/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$712万
-$25,335/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$701万
-$24,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,369万
-$25,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$909万
-$22,774/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,551万
-$25,385/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$895万
-$25,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$597万
-$21,307/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$651万
-$25,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$940万
-$25,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N19" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$756万
-$20,042/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O19" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,083万
-$25,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q19" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$538万
-$25,263/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R19" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$961万
-$24,636/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S19" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$924万
-$25,944/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$692万
-$24,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 268呎 (开放式)
-$645万
-$24,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$871万
-$31,121/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$677万
-$24,082/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$671万
-$23,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,311万
-$24,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$904万
-$22,662/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,837万
-$30,070/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$877万
-$25,195/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$585万
-$20,882/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$626万
-$24,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$933万
-$25,553/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N20" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$674万
-$17,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O20" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,075万
-$25,539/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q20" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$520万
-$24,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R20" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$960万
-$24,626/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S20" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$938万
-$26,337/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$689万
-$24,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$623万
-$23,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$867万
-$30,968/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$673万
-$23,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$668万
-$23,677/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,304万
-$24,240/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$900万
-$22,546/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,170万
-$19,149/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$877万
-$25,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$582万
-$20,775/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$605万
-$23,367/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$928万
-$25,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$979万
-$25,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$1,001万
-$23,784/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P21" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q21" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$517万
-$24,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R21" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$956万
-$24,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S21" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$874万
-$24,542/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$685万
-$24,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$620万
-$23,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$863万
-$30,814/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$670万
-$23,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$664万
-$23,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,298万
-$24,121/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$895万
-$22,434/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,819万
-$29,769/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$842万
-$24,195/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$579万
-$20,675/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$617万
-$23,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$923万
-$25,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$702万
-$18,621/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$996万
-$23,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P22" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q22" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$515万
-$24,178/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R22" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$918万
-$23,538/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S22" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$869万
-$24,419/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$652万
-$23,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 268呎 (开放式)
-$620万
-$23,119/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$862万
-$30,786/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$669万
-$23,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$664万
-$23,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,296万
-$24,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$894万
-$22,411/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,817万
-$29,741/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$841万
-$24,170/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$578万
-$20,657/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$602万
-$23,236/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$922万
-$25,271/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$690万
-$18,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$995万
-$23,644/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P23" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q23" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$514万
-$24,150/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R23" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$917万
-$23,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S23" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$868万
-$24,393/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$692万
-$24,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$730万
-$27,360/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$853万
-$30,479/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$663万
-$23,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$657万
-$23,298/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,283万
-$23,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$885万
-$22,188/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,799万
-$29,444/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$833万
-$23,931/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$573万
-$20,450/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$596万
-$23,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$913万
-$25,019/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$694万
-$18,416/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O24" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$986万
-$23,409/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q24" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$511万
-$23,986/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R24" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$943万
-$24,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S24" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$860万
-$24,149/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>N1 | 280呎 (1房)
-$642万
-$22,943/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$611万
-$22,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>N2 | 280呎 (1房)
-$849万
-$30,325/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>N3 | 281呎 (1房)
-$758万
-$26,972/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 282呎 (1房)
-$654万
-$23,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>N6 | 538呎 (3房)
-$1,277万
-$23,736/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>N7 | 399呎 (2房)
-$881万
-$22,078/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>N8 | 611呎 (3房)
-$1,504万
-$24,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 348呎 (2房)
-$858万
-$24,661/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>S1 | 280呎 (1房)
-$570万
-$20,346/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$593万
-$22,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 365呎 (2房)
-$909万
-$24,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
-        <is>
-          <t>S3 | 377呎 (2房)
-$656万
-$17,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>S5 | 421呎 (2房)
-$981万
-$23,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q25" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 213呎 (开放式)
-$510万
-$23,939/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R25" s="18" t="inlineStr">
-        <is>
-          <t>S8 | 390呎 (2房)
-$909万
-$23,303/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S25" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$886万
-$24,890/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>N1 | 242呎 (1房)
-$899万
-$37,157/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>N10 | 267呎 (开放式)
-$608万
-$22,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>N2 | 242呎 (1房)
-$895万
-$36,967/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>N3 | 243呎 (1房)
-$894万
-$36,794/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>N5 | 244呎 (1房)
-$514万
-$21,057/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>N6 | 501呎 (3房)
-$1,792万
-$35,762/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>N7 | 361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>N8 | 574呎 (3房)
-$1,946万
-$33,899/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>N9 | 310呎 (2房)
-$898万
-$28,984/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>S1 | 242呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>S10 | 259呎 (开放式)
-$590万
-$22,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="inlineStr">
-        <is>
-          <t>S2 | 328呎 (2房)
-$1,213万
-$36,973/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
-        <is>
-          <t>S3 | 339呎 (2房)
-$1,246万
-$36,752/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="O26" s="19" t="inlineStr">
-        <is>
-          <t>S5 | 384呎 (2房)
-$1,546万
-$40,258/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P26" s="16" t="inlineStr">
-        <is>
-          <t>S6 | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q26" s="18" t="inlineStr">
-        <is>
-          <t>S7 | 175呎 (开放式)
-$530万
-$30,303/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="R26" s="17" t="inlineStr">
-        <is>
-          <t>S8 | 351呎 (2房)
-$1,311万
-$37,350/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="S26" s="18" t="inlineStr">
-        <is>
-          <t>S9 | 356呎 (2房)
-$882万
-$24,764/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-长沙湾-连方II.xlsx
+++ b/files/九龙-长沙湾-连方II.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连方II" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +228,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18229,4 +18416,3382 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:S25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>连方II 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S5" s="20" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$875万
+$31,254/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 268呎 (开放式)
+$607万
+$22,657/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$907万
+$32,285/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$937万
+$33,213/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1205万
+$22,401/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$960万
+$27,589/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$586万
+$22,625/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$1243万
+$34,066/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1461万
+$34,701/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$431万
+$20,244/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1047万
+$26,838/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$696万
+$19,556/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$862万
+$30,793/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$507万
+$18,985/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$894万
+$31,804/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$563万
+$19,965/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1199万
+$22,292/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$946万
+$27,184/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$583万
+$22,514/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$1225万
+$33,564/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1439万
+$34,185/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$411万
+$19,315/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1031万
+$26,441/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="S7" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$1000万
+$28,087/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$858万
+$30,643/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$586万
+$21,963/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$889万
+$31,651/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$797万
+$28,266/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1193万
+$22,180/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$941万
+$27,049/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$499万
+$19,266/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M8" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$778万
+$21,301/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1427万
+$33,903/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$409万
+$19,216/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1026万
+$26,313/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="S8" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$995万
+$27,944/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$743万
+$26,525/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$502万
+$18,798/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$868万
+$30,883/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$615万
+$21,823/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1187万
+$22,071/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$937万
+$26,914/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$485万
+$18,730/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$693万
+$18,978/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1415万
+$33,620/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$404万
+$18,972/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="R9" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1021万
+$26,182/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$967万
+$27,160/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$764万
+$27,304/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$488万
+$18,270/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$864万
+$30,730/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$770万
+$27,316/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$992万
+$18,446/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$932万
+$26,779/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$483万
+$18,633/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$764万
+$20,945/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$735万
+$19,488/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$807万
+$19,166/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$523万
+$24,540/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1016万
+$26,054/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="S10" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$962万
+$27,028/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$735万
+$26,264/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$697万
+$26,120/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$640万
+$22,857/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$748万
+$26,605/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$879万
+$31,160/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1443万
+$26,816/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1608万
+$26,313/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$927万
+$26,649/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$674万
+$26,023/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$681万
+$18,660/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$756万
+$20,066/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1147万
+$27,247/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$520万
+$24,423/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="R11" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1035万
+$26,541/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="S11" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$980万
+$27,531/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$825万
+$29,454/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$678万
+$25,386/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$637万
+$22,743/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$641万
+$22,822/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$759万
+$26,911/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$983万
+$18,264/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1095万
+$17,923/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$923万
+$26,514/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$671万
+$25,896/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$987万
+$27,030/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$846万
+$22,432/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1138万
+$27,021/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$518万
+$24,305/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1006万
+$25,795/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$953万
+$26,758/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$730万
+$26,082/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$674万
+$25,262/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$634万
+$22,632/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$740万
+$26,342/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$770万
+$27,319/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1428万
+$26,548/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1090万
+$17,835/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$918万
+$26,385/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$667万
+$25,768/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$978万
+$26,808/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="N13" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$1033万
+$27,390/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="O13" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1128万
+$26,791/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q13" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$515万
+$24,188/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="R13" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1001万
+$25,667/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="S13" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$948万
+$26,626/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$820万
+$29,275/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$674万
+$25,236/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$921万
+$32,889/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$850万
+$30,249/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$750万
+$26,613/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$977万
+$18,154/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1893万
+$30,987/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$917万
+$26,359/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$667万
+$25,741/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$974万
+$26,685/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$704万
+$18,666/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1150万
+$27,306/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$399万
+$18,742/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1000万
+$25,644/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$970万
+$27,233/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$706万
+$25,221/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$667万
+$24,996/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$912万
+$32,561/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$732万
+$26,053/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$727万
+$25,777/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1413万
+$26,260/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1134万
+$18,561/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$908万
+$26,101/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$786万
+$30,359/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$961万
+$26,332/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$773万
+$20,496/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1108万
+$26,321/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q15" s="24" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$660万
+$30,967/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="R15" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$990万
+$25,390/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$938万
+$26,340/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$703万
+$25,096/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$664万
+$24,880/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$907万
+$32,400/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$729万
+$25,929/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$721万
+$25,582/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1406万
+$26,130/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$771万
+$19,326/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1567万
+$25,642/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$904万
+$25,968/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$609万
+$21,739/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$657万
+$25,375/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$954万
+$26,134/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$1007万
+$26,700/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1100万
+$26,121/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q16" s="24" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$656万
+$30,812/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="R16" s="24" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$1173万
+$30,069/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$933万
+$26,208/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$699万
+$24,971/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 268呎 (开放式)
+$661万
+$24,668/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$903万
+$32,239/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$725万
+$25,797/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$757万
+$26,848/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1399万
+$25,998/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$913万
+$22,890/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1559万
+$25,514/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$899万
+$25,839/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$606万
+$21,632/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$654万
+$25,251/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$947万
+$25,940/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$684万
+$18,146/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1092万
+$25,926/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$549万
+$25,765/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R17" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$980万
+$25,136/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S17" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$928万
+$26,076/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$696万
+$24,846/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$658万
+$24,640/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$889万
+$31,757/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$712万
+$25,335/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$701万
+$24,858/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1369万
+$25,452/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$909万
+$22,774/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1551万
+$25,385/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$895万
+$25,710/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$597万
+$21,307/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$651万
+$25,127/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$940万
+$25,742/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$756万
+$20,042/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1083万
+$25,732/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$538万
+$25,263/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$961万
+$24,636/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$924万
+$25,944/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$692万
+$24,721/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 268呎 (开放式)
+$645万
+$24,071/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$871万
+$31,121/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$677万
+$24,082/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$671万
+$23,794/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1311万
+$24,362/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$904万
+$22,662/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1837万
+$30,070/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$877万
+$25,195/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$585万
+$20,882/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$626万
+$24,185/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$933万
+$25,553/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$674万
+$17,873/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1075万
+$25,539/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q19" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$520万
+$24,408/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R19" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$960万
+$24,626/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S19" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$938万
+$26,337/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$689万
+$24,596/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$623万
+$23,341/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$867万
+$30,968/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$673万
+$23,964/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$668万
+$23,677/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1304万
+$24,240/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$900万
+$22,546/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1170万
+$19,149/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$877万
+$25,193/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$582万
+$20,775/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$605万
+$23,367/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$928万
+$25,425/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$979万
+$25,979/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$1001万
+$23,784/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$517万
+$24,286/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R20" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$956万
+$24,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$874万
+$24,542/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$685万
+$24,479/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$620万
+$23,232/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$863万
+$30,814/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$670万
+$23,843/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$664万
+$23,560/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1298万
+$24,121/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$895万
+$22,434/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1819万
+$29,769/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$842万
+$24,195/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$579万
+$20,675/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$617万
+$23,811/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$923万
+$25,296/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$702万
+$18,621/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O21" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$996万
+$23,667/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="P21" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$515万
+$24,178/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R21" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$918万
+$23,538/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S21" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$869万
+$24,419/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$652万
+$23,296/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 268呎 (开放式)
+$620万
+$23,119/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$862万
+$30,786/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$669万
+$23,822/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$664万
+$23,535/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1296万
+$24,095/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$894万
+$22,411/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1817万
+$29,741/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$841万
+$24,170/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$578万
+$20,657/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$602万
+$23,236/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$922万
+$25,271/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$690万
+$18,292/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$995万
+$23,644/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$514万
+$24,150/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$917万
+$23,515/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="S22" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$868万
+$24,393/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$692万
+$24,707/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$730万
+$27,360/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$853万
+$30,479/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$663万
+$23,584/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$657万
+$23,298/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1283万
+$23,855/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$885万
+$22,188/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1799万
+$29,444/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$833万
+$23,931/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$573万
+$20,450/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$596万
+$23,012/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$913万
+$25,019/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$694万
+$18,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$986万
+$23,409/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q23" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$511万
+$23,986/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R23" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$943万
+$24,185/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S23" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$860万
+$24,149/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>N1 | 280呎 (1房)
+$642万
+$22,943/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$611万
+$22,869/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>N2 | 280呎 (1房)
+$849万
+$30,325/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>N3 | 281呎 (1房)
+$758万
+$26,972/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 282呎 (1房)
+$654万
+$23,188/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>N6 | 538呎 (3房)
+$1277万
+$23,736/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>N7 | 399呎 (2房)
+$881万
+$22,078/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>N8 | 611呎 (3房)
+$1504万
+$24,610/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 348呎 (2房)
+$858万
+$24,661/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>S1 | 280呎 (1房)
+$570万
+$20,346/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$593万
+$22,900/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 365呎 (2房)
+$909万
+$24,896/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>S3 | 377呎 (2房)
+$656万
+$17,414/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>S5 | 421呎 (2房)
+$981万
+$23,292/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 213呎 (开放式)
+$510万
+$23,939/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="R24" s="22" t="inlineStr">
+        <is>
+          <t>S8 | 390呎 (2房)
+$909万
+$23,303/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="S24" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$886万
+$24,890/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>N1 | 242呎 (1房)
+$899万
+$37,157/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>N10 | 267呎 (开放式)
+$608万
+$22,760/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>N2 | 242呎 (1房)
+$895万
+$36,967/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>N3 | 243呎 (1房)
+$894万
+$36,794/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>N5 | 244呎 (1房)
+$514万
+$21,057/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>N6 | 501呎 (3房)
+$1792万
+$35,762/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>N7 | 361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>N8 | 574呎 (3房)
+$1946万
+$33,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>N9 | 310呎 (2房)
+$898万
+$28,984/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>S1 | 242呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>S10 | 259呎 (开放式)
+$590万
+$22,788/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 328呎 (2房)
+$1213万
+$36,973/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>S3 | 339呎 (2房)
+$1246万
+$36,752/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="O25" s="23" t="inlineStr">
+        <is>
+          <t>S5 | 384呎 (2房)
+$1546万
+$40,258/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>S6 | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q25" s="22" t="inlineStr">
+        <is>
+          <t>S7 | 175呎 (开放式)
+$530万
+$30,303/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="R25" s="21" t="inlineStr">
+        <is>
+          <t>S8 | 351呎 (2房)
+$1311万
+$37,350/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="S25" s="22" t="inlineStr">
+        <is>
+          <t>S9 | 356呎 (2房)
+$882万
+$24,764/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-长沙湾-连方II.xlsx
+++ b/files/九龙-长沙湾-连方II.xlsx
@@ -661,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-长沙湾-连方II.xlsx
+++ b/files/九龙-长沙湾-连方II.xlsx
@@ -2307,14 +2307,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>8473220</v>
+        <v>10664570</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>20126</v>
+        <v>25332</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>7211720</v>
+        <v>9325500</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>19758</v>
+        <v>25549</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2897,18 +2897,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>5432280</v>
+        <v>7445970</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>19263</v>
+        <v>26404</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -2959,18 +2959,18 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>5261760</v>
+        <v>6804000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>18725</v>
+        <v>24214</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3153,18 +3153,18 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5075580</v>
+        <v>6782025</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>18127</v>
+        <v>24222</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>8347360</v>
+        <v>10506160</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>19827</v>
+        <v>24955</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3603,14 +3603,14 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>7105580</v>
+        <v>9188250</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>19467</v>
+        <v>25173</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -4123,18 +4123,18 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>5183460</v>
+        <v>6702750</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>18446</v>
+        <v>23853</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4317,18 +4317,18 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>5000760</v>
+        <v>6682050</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>17860</v>
+        <v>23864</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>8278340</v>
+        <v>10419290</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>19664</v>
+        <v>24749</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -5287,18 +5287,18 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5158520</v>
+        <v>6670500</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>18358</v>
+        <v>23738</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -5481,18 +5481,18 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>4976400</v>
+        <v>6649500</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>17773</v>
+        <v>23748</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5799,14 +5799,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>8209320</v>
+        <v>10332420</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>19500</v>
+        <v>24543</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6451,18 +6451,18 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>5033240</v>
+        <v>6508500</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>17912</v>
+        <v>23162</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -7607,18 +7607,18 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>5008300</v>
+        <v>6476250</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>17823</v>
+        <v>23047</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -8693,18 +8693,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>5096460</v>
+        <v>6722055</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>18073</v>
+        <v>23837</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8817,18 +8817,18 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="5" t="n">
-        <v>3712000</v>
+        <v>6368000</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>13257</v>
+        <v>22743</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -9957,18 +9957,18 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>3693440</v>
+        <v>6336160</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>13191</v>
+        <v>22629</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
@@ -10081,18 +10081,18 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>4783260</v>
+        <v>6473895</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>17083</v>
+        <v>23121</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -11097,18 +11097,18 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>3675460</v>
+        <v>6305315</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>13127</v>
+        <v>22519</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11919,14 +11919,14 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>10981140</v>
+        <v>13821090</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>17972</v>
+        <v>22620</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -12175,18 +12175,18 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>4930000</v>
+        <v>6375000</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>17544</v>
+        <v>22687</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -12237,18 +12237,18 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>5341220</v>
+        <v>6722570</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>19076</v>
+        <v>24009</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12361,18 +12361,18 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>4754260</v>
+        <v>6434645</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>16980</v>
+        <v>22981</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -12547,14 +12547,14 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>3825680</v>
+        <v>5507660</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>17961</v>
+        <v>25858</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12865,14 +12865,14 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>4560540</v>
+        <v>6251085</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>17608</v>
+        <v>24135</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13377,18 +13377,18 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>5287860</v>
+        <v>6655410</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>18885</v>
+        <v>23769</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13625,18 +13625,18 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K202" s="5" t="n">
-        <v>6801660</v>
+        <v>9322965</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>17440</v>
+        <v>23905</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位 )</t>
         </is>
       </c>
       <c r="N202" s="3" t="inlineStr">
@@ -13687,14 +13687,14 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K203" s="5" t="n">
-        <v>3806540</v>
+        <v>5480105</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>17871</v>
+        <v>25728</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -14067,18 +14067,18 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K209" s="5" t="n">
-        <v>3530460</v>
+        <v>6056565</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>12609</v>
+        <v>21631</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14501,18 +14501,18 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K216" s="5" t="n">
-        <v>5261760</v>
+        <v>6622560</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>18792</v>
+        <v>23652</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -15191,18 +15191,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>3513060</v>
+        <v>6026715</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>12547</v>
+        <v>21524</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15377,18 +15377,18 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K230" s="5" t="n">
-        <v>5297140</v>
+        <v>9087335</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>13276</v>
+        <v>22775</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -15625,18 +15625,18 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
-        <v>5235660</v>
+        <v>6589710</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>18699</v>
+        <v>23535</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -16315,18 +16315,18 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>3460280</v>
+        <v>5936170</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>12358</v>
+        <v>21201</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -16501,18 +16501,18 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>5270460</v>
+        <v>9041565</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>13209</v>
+        <v>22661</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -16749,18 +16749,18 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K252" s="5" t="n">
-        <v>5157360</v>
+        <v>6491160</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>18419</v>
+        <v>23183</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
@@ -17439,18 +17439,18 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>3391260</v>
+        <v>5817765</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>12112</v>
+        <v>20778</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -17563,18 +17563,18 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>10656340</v>
+        <v>13412290</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>17441</v>
+        <v>21951</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位)</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
@@ -17625,18 +17625,18 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>5244360</v>
+        <v>8996790</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>13144</v>
+        <v>22548</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -17873,18 +17873,18 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K270" s="5" t="n">
-        <v>5054120</v>
+        <v>6361220</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>18050</v>
+        <v>22719</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -18563,18 +18563,18 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>3373860</v>
+        <v>5787915</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>12050</v>
+        <v>20671</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -18749,18 +18749,18 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K284" s="5" t="n">
-        <v>5217680</v>
+        <v>8951020</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>13077</v>
+        <v>22434</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -18997,18 +18997,18 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K288" s="5" t="n">
-        <v>5029180</v>
+        <v>6329830</v>
       </c>
       <c r="L288" s="5" t="n">
-        <v>17961</v>
+        <v>22607</v>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
@@ -19687,18 +19687,18 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K299" s="5" t="n">
-        <v>3357620</v>
+        <v>5760055</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>11992</v>
+        <v>20572</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N299" s="3" t="inlineStr">
@@ -19811,18 +19811,18 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K301" s="5" t="n">
-        <v>10549620</v>
+        <v>13277970</v>
       </c>
       <c r="L301" s="5" t="n">
-        <v>17266</v>
+        <v>21732</v>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位 )</t>
         </is>
       </c>
       <c r="N301" s="3" t="inlineStr">
@@ -19873,18 +19873,18 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
-        <v>5191580</v>
+        <v>8906245</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>13011</v>
+        <v>22321</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N302" s="3" t="inlineStr">
@@ -20121,18 +20121,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>5004240</v>
+        <v>6298440</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>17872</v>
+        <v>22494</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20811,18 +20811,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>3354720</v>
+        <v>5755080</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>11981</v>
+        <v>20554</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20935,18 +20935,18 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K319" s="5" t="n">
-        <v>10539760</v>
+        <v>13265560</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>17250</v>
+        <v>21711</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位 )</t>
         </is>
       </c>
       <c r="N319" s="3" t="inlineStr">
@@ -20997,18 +20997,18 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K320" s="5" t="n">
-        <v>5186360</v>
+        <v>8897290</v>
       </c>
       <c r="L320" s="5" t="n">
-        <v>12998</v>
+        <v>22299</v>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -21245,18 +21245,18 @@
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K324" s="5" t="n">
-        <v>4999600</v>
+        <v>6292600</v>
       </c>
       <c r="L324" s="5" t="n">
-        <v>17856</v>
+        <v>22474</v>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
@@ -21935,18 +21935,18 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>3321080</v>
+        <v>5697370</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>11861</v>
+        <v>20348</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22059,18 +22059,18 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K337" s="5" t="n">
-        <v>10434200</v>
+        <v>13132700</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>17077</v>
+        <v>21494</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位 )</t>
         </is>
       </c>
       <c r="N337" s="3" t="inlineStr">
@@ -22121,18 +22121,18 @@
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K338" s="5" t="n">
-        <v>5134740</v>
+        <v>8808735</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>12869</v>
+        <v>22077</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N338" s="3" t="inlineStr">
@@ -22369,18 +22369,18 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>4949720</v>
+        <v>6229820</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>17678</v>
+        <v>22249</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22431,18 +22431,18 @@
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K343" s="5" t="n">
-        <v>4236900</v>
+        <v>5807475</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>15869</v>
+        <v>21751</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(不適用于N1單位)</t>
         </is>
       </c>
       <c r="N343" s="3" t="inlineStr">
@@ -23059,18 +23059,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>3304260</v>
+        <v>5668515</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>11801</v>
+        <v>20245</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -23245,18 +23245,18 @@
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K356" s="5" t="n">
-        <v>5109220</v>
+        <v>8764955</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>12805</v>
+        <v>21967</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N356" s="3" t="inlineStr">
@@ -23431,18 +23431,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>4395820</v>
+        <v>5305300</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>15643</v>
+        <v>18880</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃(只適用于N1、N3、N5單位 )</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23493,18 +23493,18 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>4924780</v>
+        <v>6198430</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>17588</v>
+        <v>22137</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -23741,18 +23741,18 @@
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K364" s="5" t="n">
-        <v>7603800</v>
+        <v>9570300</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>21663</v>
+        <v>27266</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
@@ -23935,18 +23935,18 @@
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K367" s="5" t="n">
-        <v>8966220</v>
+        <v>11285070</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>23350</v>
+        <v>29388</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N367" s="3" t="inlineStr">
@@ -23997,18 +23997,18 @@
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>7226220</v>
+        <v>9095070</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>21316</v>
+        <v>26829</v>
       </c>
       <c r="M368" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N368" s="3" t="inlineStr">
@@ -24059,18 +24059,18 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>7033660</v>
+        <v>8852710</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>21444</v>
+        <v>26990</v>
       </c>
       <c r="M369" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N369" s="3" t="inlineStr">
@@ -24315,18 +24315,18 @@
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K373" s="5" t="n">
-        <v>11285640</v>
+        <v>14204340</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>19661</v>
+        <v>24746</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N373" s="3" t="inlineStr">
@@ -24447,18 +24447,18 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K375" s="5" t="n">
-        <v>10391860</v>
+        <v>13079410</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>20742</v>
+        <v>26107</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N375" s="3" t="inlineStr">
@@ -24571,18 +24571,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>5185780</v>
+        <v>6526930</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>21341</v>
+        <v>26860</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -24633,18 +24633,18 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>5188680</v>
+        <v>6530580</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>21441</v>
+        <v>26986</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -24757,18 +24757,18 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>5215360</v>
+        <v>6564160</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>21551</v>
+        <v>27125</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃(不適用於N1、N3及N5單位 )</t>
+          <t>120天即供付款計劃</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
